--- a/opex_tool_frontend/public/examples/imports_paraugs.xlsx
+++ b/opex_tool_frontend/public/examples/imports_paraugs.xlsx
@@ -1551,7 +1551,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    DOK = dokuments (ieraksts) — tikai tekstuālos elektroniskos uzskaites sarakstos</t>
+          <t xml:space="preserve">    DOK = dokuments — tikai tekstuālos elektroniskos uzskaites sarakstos</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>GV = glabājamā vienība, DOK = dokuments (ieraksts). Obligāta katrai rindai.</t>
+          <t>GV = glabājamā vienība, DOK = dokuments. Obligāta katrai rindai.</t>
         </is>
       </c>
     </row>
